--- a/config/tutorial_DL.xlsx
+++ b/config/tutorial_DL.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schir\OneDrive\Studium\34_Github\TherMOS\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F8622A-8E0E-411A-9373-B5C51A9DF58C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-18120" yWindow="-2550" windowWidth="18240" windowHeight="28440" activeTab="1" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="1" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
